--- a/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0002T0006Z000C1N4_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0002T0006Z000C1N4_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>32.93002197890382</v>
+        <v>5.351128571571871</v>
       </c>
       <c r="D2" t="n">
-        <v>43.63285364957083</v>
+        <v>7.090338718055261</v>
       </c>
       <c r="E2" t="n">
-        <v>12.88101576100663</v>
+        <v>2.093165061163577</v>
       </c>
       <c r="F2" t="n">
-        <v>8.513104247529835</v>
+        <v>1.383379440223599</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>58.69205350091708</v>
+        <v>9.537458693899024</v>
       </c>
       <c r="D3" t="n">
-        <v>60.6590621446305</v>
+        <v>9.857097598502458</v>
       </c>
       <c r="E3" t="n">
-        <v>12.88101576100663</v>
+        <v>2.093165061163577</v>
       </c>
       <c r="F3" t="n">
-        <v>8.513104247529835</v>
+        <v>1.383379440223599</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
